--- a/samples/fixtures/xlsx/schedule-4site.xlsx
+++ b/samples/fixtures/xlsx/schedule-4site.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,6 +432,16 @@
           <t>Sprinklered</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Alarm</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>YearBuilt</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -447,6 +457,14 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>hardwired</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>2010</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -462,6 +480,14 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2007</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -477,6 +503,14 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>hardwired</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2015</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -491,6 +525,14 @@
         <is>
           <t>yes</t>
         </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>hardwired</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2018</v>
       </c>
     </row>
   </sheetData>
